--- a/experiments/Quad Model.xlsx
+++ b/experiments/Quad Model.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFB6764-6511-1C4A-8626-C4DB194B3120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEA46E9-95F2-E94E-BE92-D60E83FB020A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16660" yWindow="9220" windowWidth="28040" windowHeight="17440" xr2:uid="{0306178C-196F-A949-83BA-7B27B23D98CE}"/>
+    <workbookView xWindow="11260" yWindow="6560" windowWidth="35340" windowHeight="19900" xr2:uid="{0306178C-196F-A949-83BA-7B27B23D98CE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Formulation" sheetId="6" r:id="rId1"/>
-    <sheet name="Actual Model" sheetId="1" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1 predictions" sheetId="4" r:id="rId4"/>
+    <sheet name="Products" sheetId="6" r:id="rId1"/>
+    <sheet name="Targets" sheetId="7" r:id="rId2"/>
+    <sheet name="xxx Actual Model" sheetId="1" r:id="rId3"/>
+    <sheet name="xxx predictions" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="109">
   <si>
     <t>Input 1</t>
   </si>
@@ -309,13 +309,70 @@
   </si>
   <si>
     <t>Final volume adjustment and stabilization with remaining liquids.</t>
+  </si>
+  <si>
+    <t>Sheet 3: Testing Equipment Description</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Performance Metric</t>
+  </si>
+  <si>
+    <t>Equipment (Brand &amp; Type)</t>
+  </si>
+  <si>
+    <t>Appearance (Color Accuracy &amp; Consistency)</t>
+  </si>
+  <si>
+    <t>X-Rite Ci64 Spectrophotometer</t>
+  </si>
+  <si>
+    <t>Quantifies color and ΔE to ensure batch-to-batch consistency and match to target shade specifications.</t>
+  </si>
+  <si>
+    <t>Appearance (Gloss / Sheen)</t>
+  </si>
+  <si>
+    <t>BYK-Gardner micro-TRI-gloss Meter</t>
+  </si>
+  <si>
+    <t>Measures gloss at multiple angles (20°, 60°, 85°) to characterize finish (matte to high gloss) and detect surface defects.</t>
+  </si>
+  <si>
+    <t>Durability (Abrasion Resistance)</t>
+  </si>
+  <si>
+    <t>Taber Industries Model 5135 Taber Abraser</t>
+  </si>
+  <si>
+    <t>Simulates mechanical wear to assess coating resistance to scratching, scuffing, and erosion over time.</t>
+  </si>
+  <si>
+    <t>Application (Viscosity / Flow Behavior)</t>
+  </si>
+  <si>
+    <t>Brookfield DV2T Viscometer</t>
+  </si>
+  <si>
+    <t>Measures viscosity and rheology, informing application properties like leveling, sag resistance, and ease of brushing or spraying.</t>
+  </si>
+  <si>
+    <t>Long-Term Stability (Weathering Resistance)</t>
+  </si>
+  <si>
+    <t>Q-Lab QUV/se Accelerated Weathering Tester</t>
+  </si>
+  <si>
+    <t>Exposes coatings to UV, moisture, and heat cycles to predict fading, chalking, and degradation in real-world environments.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -362,8 +419,34 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -382,8 +465,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -391,19 +480,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -413,11 +518,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -441,6 +581,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -465,6 +606,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -489,6 +631,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -513,6 +656,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -537,6 +681,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -561,6 +706,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -585,6 +731,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -609,6 +756,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -633,6 +781,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -657,6 +806,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -681,6 +831,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -705,6 +856,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -729,6 +881,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -753,6 +906,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -777,6 +931,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -801,6 +956,7 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -825,6 +981,136 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF0A0A0A"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF0A0A0A"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color rgb="FF0A0A0A"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -941,30 +1227,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6F4D116D-1E0A-714D-A7D2-B44326FD3112}" name="Table3" displayName="Table3" ref="A3:O23" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6F4D116D-1E0A-714D-A7D2-B44326FD3112}" name="Table3" displayName="Table3" ref="A3:O23" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
   <autoFilter ref="A3:O23" xr:uid="{6F4D116D-1E0A-714D-A7D2-B44326FD3112}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{33E290FC-C296-C447-84A2-5DA13F82EA53}" name="Formulation ID" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{B12C3E61-A0D7-2543-92EF-AC65FB4B5FAF}" name="Resin (g)" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{4E3E8FA4-439D-D84C-8820-9B7467C2577D}" name="Solvent (g)" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{94EDF2B6-8027-6E45-A099-E409C349D419}" name="Pigment (g)" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{60145BF4-4648-FC4A-B0FD-6260680FEF99}" name="Additives (g)" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{8CFD3AC9-DA14-3740-B3D6-CCEEDDB70A33}" name="Extender (g)" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{063E9EDF-E1A7-1E45-B96F-415B991769F9}" name="Prepared By" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{DB1B480E-60C9-2F44-80FD-72A812081698}" name="Color" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{648C6F3E-F4AA-9140-BB45-CFFDAC1FC593}" name="Viscosity (KU)" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{F9C5A839-7652-F942-9E8F-2C15180F8314}" name="Dry Time (min)" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{BC14BBD2-0299-A840-8B78-6FB1F18B9DCE}" name="Adhesion (0-5B)" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{C5834ADB-0307-5844-AFF7-FAF8B4AB10C9}" name="Gloss (60°)" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{D329EAF0-3832-9F43-A539-F861D2C392C7}" name="Opacity (%)" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{CE540A47-F851-084D-81F4-E22A35EA2E2D}" name="Finish Type" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{4653D141-3ABF-0243-9932-DCDB5CDD11D5}" name="Application Grade" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{33E290FC-C296-C447-84A2-5DA13F82EA53}" name="Formulation ID" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{B12C3E61-A0D7-2543-92EF-AC65FB4B5FAF}" name="Resin (g)" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{4E3E8FA4-439D-D84C-8820-9B7467C2577D}" name="Solvent (g)" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{94EDF2B6-8027-6E45-A099-E409C349D419}" name="Pigment (g)" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{60145BF4-4648-FC4A-B0FD-6260680FEF99}" name="Additives (g)" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{8CFD3AC9-DA14-3740-B3D6-CCEEDDB70A33}" name="Extender (g)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{063E9EDF-E1A7-1E45-B96F-415B991769F9}" name="Prepared By" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{DB1B480E-60C9-2F44-80FD-72A812081698}" name="Color" dataDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{648C6F3E-F4AA-9140-BB45-CFFDAC1FC593}" name="Viscosity (KU)" dataDxfId="9"/>
+    <tableColumn id="10" xr3:uid="{F9C5A839-7652-F942-9E8F-2C15180F8314}" name="Dry Time (min)" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{BC14BBD2-0299-A840-8B78-6FB1F18B9DCE}" name="Adhesion (0-5B)" dataDxfId="7"/>
+    <tableColumn id="12" xr3:uid="{C5834ADB-0307-5844-AFF7-FAF8B4AB10C9}" name="Gloss (60°)" dataDxfId="6"/>
+    <tableColumn id="13" xr3:uid="{D329EAF0-3832-9F43-A539-F861D2C392C7}" name="Opacity (%)" dataDxfId="5"/>
+    <tableColumn id="14" xr3:uid="{CE540A47-F851-084D-81F4-E22A35EA2E2D}" name="Finish Type" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{4653D141-3ABF-0243-9932-DCDB5CDD11D5}" name="Application Grade" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7E13B7F9-EEA1-B14E-9EF4-EE2B51F53600}" name="Table6" displayName="Table6" ref="A37:C42" totalsRowShown="0" headerRowDxfId="21" dataDxfId="22">
+  <autoFilter ref="A37:C42" xr:uid="{7E13B7F9-EEA1-B14E-9EF4-EE2B51F53600}"/>
+  <tableColumns count="3">
+    <tableColumn id="2" xr3:uid="{82D64CC9-EACF-084D-B95F-2BFCBFD61A12}" name="Equipment (Brand &amp; Type)" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DC9D2881-6106-214E-9715-2B5B63544E21}" name="Performance Metric" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{967E22C7-52BE-7A4C-B0C2-929AA4A708C4}" name="Description" dataDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{5695F8C1-7988-1E46-8A58-977814439D73}" name="Table7" displayName="Table7" ref="A28:C33" totalsRowShown="0">
+  <autoFilter ref="A28:C33" xr:uid="{5695F8C1-7988-1E46-8A58-977814439D73}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{95B8C609-CEB1-CE4D-8114-23AAFA15F489}" name="Step" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{95057C7D-3FD2-A745-8D9D-3CE170938A2B}" name="Phase" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{E55AAD89-4E77-604A-9A0C-5F2D930AEDB5}" name="Action Description" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{10E50C0E-D991-804D-92B8-9D9193E8DF60}" name="Table1" displayName="Table1" ref="A1:G10" totalsRowShown="0">
   <autoFilter ref="A1:G10" xr:uid="{10E50C0E-D991-804D-92B8-9D9193E8DF60}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G10">
@@ -975,13 +1285,13 @@
     <tableColumn id="7" xr3:uid="{3CAE235D-1989-6F42-A60A-7B8FC8A774D3}" name="Input 1"/>
     <tableColumn id="2" xr3:uid="{3CC7D3F3-D561-F043-937C-695DE9C18BDB}" name="Input 2"/>
     <tableColumn id="3" xr3:uid="{DACB5751-FBCB-7347-8B51-F87D769CD468}" name="Input 3"/>
-    <tableColumn id="4" xr3:uid="{9DE2D8C8-195F-0F4F-9F59-51810DD0CA30}" name="Output 1" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{9DE2D8C8-195F-0F4F-9F59-51810DD0CA30}" name="Output 1" dataDxfId="42">
       <calculatedColumnFormula>B2*0.3 + C2*0.5 - D2*10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{A1D8645A-5258-0642-BCE2-050B3B9F789B}" name="Output 2" dataDxfId="33">
+    <tableColumn id="5" xr3:uid="{A1D8645A-5258-0642-BCE2-050B3B9F789B}" name="Output 2" dataDxfId="41">
       <calculatedColumnFormula>B2*C2*D2-B2-D2*C2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4D5E4DA2-A09F-5741-B645-DA2A0EBF29EC}" name="Output 3" dataDxfId="32">
+    <tableColumn id="6" xr3:uid="{4D5E4DA2-A09F-5741-B645-DA2A0EBF29EC}" name="Output 3" dataDxfId="40">
       <calculatedColumnFormula>INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -989,23 +1299,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C58DDC07-B596-154D-B441-E400DBADF2D6}" name="Table2" displayName="Table2" ref="A1:M10" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C58DDC07-B596-154D-B441-E400DBADF2D6}" name="Table2" displayName="Table2" ref="A1:M10" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:M10" xr:uid="{C58DDC07-B596-154D-B441-E400DBADF2D6}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{91B587A9-47FD-C547-A43E-E54A24DD4070}" name="ROW NUM" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{F7B86DD5-682B-F24A-997C-3CFE85977327}" name="Input 1" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{DF8ECEDF-3D7E-F54D-9F96-F100A34D07C3}" name="Input 2" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{555CBE6E-78E3-1042-8460-7E711D306E9C}" name="Input 3" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{8ACCA02D-F444-3E45-BC44-7997AAF1DC06}" name="Output 1" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{9F8A07C5-ED18-7D4C-B183-6CEF2389C147}" name="Output 2" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{59B37B1D-3BB7-B445-8A7E-30F1DD59CE56}" name="Output 3" dataDxfId="23"/>
-    <tableColumn id="8" xr3:uid="{D1CE1D7D-93FA-184A-BBB0-75704B130758}" name="Output 1 prediction" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{9ECDBACF-2D06-3948-BF83-199ACB8933F3}" name="Output 2 prediction" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{89CC5218-4878-C049-B22D-5512D8E3038A}" name="Output 3 prediction" dataDxfId="20"/>
-    <tableColumn id="11" xr3:uid="{6BD7AA4B-4F81-D944-AD02-B3EC6CD5522A}" name="Output 1 uncertainty" dataDxfId="19"/>
-    <tableColumn id="12" xr3:uid="{11564B90-738B-034A-A983-E7ADAB73CC48}" name="Output 2 uncertainty" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{B8BA8942-F3F3-1A41-8AD5-273586AAEE9C}" name="Output 3 uncertainty" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{91B587A9-47FD-C547-A43E-E54A24DD4070}" name="ROW NUM" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{F7B86DD5-682B-F24A-997C-3CFE85977327}" name="Input 1" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{DF8ECEDF-3D7E-F54D-9F96-F100A34D07C3}" name="Input 2" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{555CBE6E-78E3-1042-8460-7E711D306E9C}" name="Input 3" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{8ACCA02D-F444-3E45-BC44-7997AAF1DC06}" name="Output 1" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{9F8A07C5-ED18-7D4C-B183-6CEF2389C147}" name="Output 2" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{59B37B1D-3BB7-B445-8A7E-30F1DD59CE56}" name="Output 3" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{D1CE1D7D-93FA-184A-BBB0-75704B130758}" name="Output 1 prediction" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{9ECDBACF-2D06-3948-BF83-199ACB8933F3}" name="Output 2 prediction" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{89CC5218-4878-C049-B22D-5512D8E3038A}" name="Output 3 prediction" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{6BD7AA4B-4F81-D944-AD02-B3EC6CD5522A}" name="Output 1 uncertainty" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{11564B90-738B-034A-A983-E7ADAB73CC48}" name="Output 2 uncertainty" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{B8BA8942-F3F3-1A41-8AD5-273586AAEE9C}" name="Output 3 uncertainty" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1348,1148 +1658,1368 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5079FFF3-CA43-814C-A594-AD8267706CA5}">
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14" style="4" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="17.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="4" customWidth="1"/>
-    <col min="9" max="9" width="19.6640625" style="4" customWidth="1"/>
-    <col min="10" max="10" width="20" style="4" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" style="4" customWidth="1"/>
-    <col min="12" max="12" width="16.1640625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="16.6640625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="17" style="4" customWidth="1"/>
-    <col min="15" max="15" width="24.1640625" style="4" customWidth="1"/>
-    <col min="16" max="16384" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="48.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.1640625" customWidth="1"/>
+    <col min="13" max="13" width="16.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
         <v>66</v>
       </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>73</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" t="s">
         <v>74</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" t="s">
         <v>67</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="O3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="17">
         <v>450</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="17">
         <v>300</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="17">
         <v>150</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="17">
         <v>20</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="17">
         <v>80</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="17">
         <v>85</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="17">
         <v>45</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="17">
         <v>88</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="17">
         <v>94</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="17">
         <v>400</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="17">
         <v>350</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="17">
         <v>120</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="17">
         <v>30</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="17">
         <v>100</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="17">
         <v>78</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="17">
         <v>38</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="17">
         <v>82</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="17">
         <v>91</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="17">
         <v>500</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="17">
         <v>250</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="17">
         <v>180</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="17">
         <v>15</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="17">
         <v>55</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="17">
         <v>92</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="17">
         <v>55</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="17">
         <v>91</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="17">
         <v>97</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="17">
         <v>350</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="17">
         <v>400</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="17">
         <v>140</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="17">
         <v>25</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="17">
         <v>85</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="17">
         <v>72</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="17">
         <v>30</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="17">
         <v>75</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="17">
         <v>89</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="17">
         <v>420</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="17">
         <v>320</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="17">
         <v>160</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="17">
         <v>20</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="17">
         <v>80</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="17">
         <v>88</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="17">
         <v>42</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="17">
         <v>85</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="17">
         <v>95</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="17">
         <v>480</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="17">
         <v>280</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="17">
         <v>130</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="17">
         <v>10</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="17">
         <v>100</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="17">
         <v>95</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="17">
         <v>60</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="17">
         <v>80</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="17">
         <v>92</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="17">
         <v>380</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="17">
         <v>370</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="17">
         <v>170</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="17">
         <v>35</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="17">
         <v>45</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="17">
         <v>80</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="17">
         <v>35</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="17">
         <v>84</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="17">
         <v>96</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="O10" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="17">
         <v>440</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="17">
         <v>310</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="17">
         <v>145</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="17">
         <v>25</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="17">
         <v>80</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="17">
         <v>84</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="17">
         <v>48</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="17">
         <v>87</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="17">
         <v>93</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="O11" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="17">
         <v>460</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="17">
         <v>290</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="17">
         <v>155</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="17">
         <v>15</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="17">
         <v>80</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="17">
         <v>90</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="17">
         <v>50</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="17">
         <v>89</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="17">
         <v>95</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="O12" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="17">
         <v>410</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="17">
         <v>340</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="17">
         <v>125</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="17">
         <v>40</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="17">
         <v>85</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="17">
         <v>76</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="17">
         <v>40</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="17">
         <v>79</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="17">
         <v>90</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="O13" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="17">
         <v>430</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="17">
         <v>330</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="17">
         <v>150</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="17">
         <v>20</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="17">
         <v>70</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="17">
         <v>82</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="17">
         <v>44</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="17">
         <v>86</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="17">
         <v>94</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="O14" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="17">
         <v>470</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="17">
         <v>270</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="17">
         <v>165</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="17">
         <v>25</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="17">
         <v>70</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="17">
         <v>98</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="17">
         <v>58</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="17">
         <v>90</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="17">
         <v>98</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="O15" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="17">
         <v>390</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="17">
         <v>360</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="17">
         <v>135</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="17">
         <v>30</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="17">
         <v>85</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="17">
         <v>79</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="17">
         <v>36</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="17">
         <v>81</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="17">
         <v>91</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="O16" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="17">
         <v>415</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="17">
         <v>325</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="17">
         <v>160</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="17">
         <v>20</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="17">
         <v>80</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="17">
         <v>86</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="17">
         <v>43</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="17">
         <v>85</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="17">
         <v>95</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="O17" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="17">
         <v>455</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="17">
         <v>305</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="17">
         <v>140</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="17">
         <v>15</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="17">
         <v>85</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="17">
         <v>89</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="17">
         <v>47</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="17">
         <v>88</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="17">
         <v>93</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O18" s="6" t="s">
+      <c r="O18" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="17">
         <v>375</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="17">
         <v>385</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="17">
         <v>145</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="17">
         <v>35</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="17">
         <v>60</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="17">
         <v>74</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="17">
         <v>32</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="17">
         <v>77</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="17">
         <v>92</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="N19" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="O19" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="17">
         <v>490</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="17">
         <v>260</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="17">
         <v>175</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="17">
         <v>10</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="17">
         <v>65</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="17">
         <v>102</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="17">
         <v>65</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="17">
         <v>92</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="17">
         <v>98</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O20" s="6" t="s">
+      <c r="O20" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="17">
         <v>425</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="17">
         <v>315</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="17">
         <v>150</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="17">
         <v>25</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="17">
         <v>85</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="17">
         <v>87</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="17">
         <v>45</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="17">
         <v>84</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="17">
         <v>94</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O21" s="6" t="s">
+      <c r="O21" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="17">
         <v>405</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="17">
         <v>345</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="17">
         <v>130</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="17">
         <v>30</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="17">
         <v>90</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="17">
         <v>77</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="17">
         <v>39</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="17">
         <v>80</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="17">
         <v>91</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="O22" s="6" t="s">
+      <c r="O22" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="17">
         <v>445</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="17">
         <v>305</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="17">
         <v>155</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="17">
         <v>20</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="17">
         <v>75</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="17">
         <v>91</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="17">
         <v>49</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="17">
         <v>87</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="17">
         <v>96</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="O23" s="6" t="s">
+      <c r="O23" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="25" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B27"/>
-      <c r="C27"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
+      <c r="A29" s="5">
         <v>1</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="6" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
+      <c r="A30" s="5">
         <v>2</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
+      <c r="A31" s="5">
         <v>3</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
+      <c r="A32" s="5">
         <v>4</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.2">
-      <c r="A33" s="9">
+    <row r="33" spans="1:8" ht="18" x14ac:dyDescent="0.2">
+      <c r="A33" s="5">
         <v>5</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="6" t="s">
         <v>89</v>
       </c>
+    </row>
+    <row r="36" spans="1:8" ht="25" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+    </row>
+    <row r="37" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42" spans="1:8" ht="19" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="3">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8F96A1-DEF1-9844-912F-85A9AE9E4E99}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="8">
+        <v>80</v>
+      </c>
+      <c r="B2" s="8">
+        <v>30</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="8">
+        <v>80</v>
+      </c>
+      <c r="E2" s="8">
+        <v>95</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
+        <v>67</v>
+      </c>
+      <c r="B3" s="3">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3">
+        <v>80</v>
+      </c>
+      <c r="E3" s="3">
+        <v>95</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>100</v>
+      </c>
+      <c r="B4" s="8">
+        <v>34</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="8">
+        <v>75</v>
+      </c>
+      <c r="E4" s="8">
+        <v>95</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642464C6-369E-D846-BCA4-2B1047987EB7}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -2537,11 +3067,11 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <f>B2*0.3 + C2*0.5 - D2*10</f>
+        <f t="shared" ref="E2:E10" si="0">B2*0.3 + C2*0.5 - D2*10</f>
         <v>-97.2</v>
       </c>
       <c r="F2">
-        <f>B2*C2*D2-B2-D2*C2</f>
+        <f t="shared" ref="F2:F10" si="1">B2*C2*D2-B2-D2*C2</f>
         <v>-1</v>
       </c>
       <c r="G2">
@@ -2563,11 +3093,11 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <f>B3*0.3 + C3*0.5 - D3*10</f>
+        <f t="shared" si="0"/>
         <v>-197.9</v>
       </c>
       <c r="F3">
-        <f>B3*C3*D3-B3-D3*C3</f>
+        <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="G3">
@@ -2589,16 +3119,16 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <f>B4*0.3 + C4*0.5 - D4*10</f>
+        <f t="shared" si="0"/>
         <v>-496.1</v>
       </c>
       <c r="F4">
-        <f>B4*C4*D4-B4-D4*C4</f>
+        <f t="shared" si="1"/>
         <v>597</v>
       </c>
       <c r="G4">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2615,11 +3145,11 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <f>B5*0.3 + C5*0.5 - D5*10</f>
+        <f t="shared" si="0"/>
         <v>-294.8</v>
       </c>
       <c r="F5">
-        <f>B5*C5*D5-B5-D5*C5</f>
+        <f t="shared" si="1"/>
         <v>716</v>
       </c>
       <c r="G5">
@@ -2641,16 +3171,16 @@
         <v>80</v>
       </c>
       <c r="E6">
-        <f>B6*0.3 + C6*0.5 - D6*10</f>
+        <f t="shared" si="0"/>
         <v>-797.5</v>
       </c>
       <c r="F6">
-        <f>B6*C6*D6-B6-D6*C6</f>
+        <f t="shared" si="1"/>
         <v>635</v>
       </c>
       <c r="G6">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2667,16 +3197,16 @@
         <v>90</v>
       </c>
       <c r="E7">
-        <f>B7*0.3 + C7*0.5 - D7*10</f>
+        <f t="shared" si="0"/>
         <v>-896.7</v>
       </c>
       <c r="F7">
-        <f>B7*C7*D7-B7-D7*C7</f>
+        <f t="shared" si="1"/>
         <v>1344</v>
       </c>
       <c r="G7">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -2693,16 +3223,16 @@
         <v>20</v>
       </c>
       <c r="E8">
-        <f>B8*0.3 + C8*0.5 - D8*10</f>
+        <f t="shared" si="0"/>
         <v>-195.4</v>
       </c>
       <c r="F8">
-        <f>B8*C8*D8-B8-D8*C8</f>
+        <f t="shared" si="1"/>
         <v>593</v>
       </c>
       <c r="G8">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -2719,16 +3249,16 @@
         <v>30</v>
       </c>
       <c r="E9">
-        <f>B9*0.3 + C9*0.5 - D9*10</f>
+        <f t="shared" si="0"/>
         <v>-294.60000000000002</v>
       </c>
       <c r="F9">
-        <f>B9*C9*D9-B9-D9*C9</f>
+        <f t="shared" si="1"/>
         <v>1252</v>
       </c>
       <c r="G9">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -2745,16 +3275,16 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <f>B10*0.3 + C10*0.5 - D10*10</f>
+        <f t="shared" si="0"/>
         <v>-293.8</v>
       </c>
       <c r="F10">
-        <f>B10*C10*D10-B10-D10*C10</f>
+        <f t="shared" si="1"/>
         <v>1671</v>
       </c>
       <c r="G10">
         <f ca="1">INT(RAND()*Table1[[#This Row],[Input 1]]  + Table1[[#This Row],[Input 2]] + Table1[[#This Row],[Input 3]])</f>
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2766,15 +3296,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C0D493D-0EBA-EC44-B99A-276BF8690E09}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
